--- a/Name.xlsx
+++ b/Name.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\我的資料_路亞國際學校\02A.電腦課程\4000 Essential English Words 題庫系統 1.0 Beta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\我的資料_路亞國際學校\02A.電腦課程\4000 Essential English Words 題庫系統 1.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5E994C1-5538-4654-A6C2-5FBDCEFB63BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{224ACEBB-53B5-4A48-8DD3-73E8ADF4F33C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7DCBFBB1-30D6-49BD-98B1-80C988443001}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="145">
   <si>
     <t>Jayden Lee</t>
   </si>
@@ -129,9 +129,6 @@
   </si>
   <si>
     <t>Aria Loh</t>
-  </si>
-  <si>
-    <t>Jasmine Pei</t>
   </si>
   <si>
     <t>Jason Tsai</t>
@@ -478,6 +475,18 @@
   </si>
   <si>
     <t>Cname</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jasmine Pei</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>盧榆方</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lucas Lu</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -539,7 +548,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -551,6 +560,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -886,7 +898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{623AE36C-F2A7-441C-93D3-E708820A8AF6}">
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.125" bestFit="1" customWidth="1"/>
@@ -895,761 +907,772 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B24" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B25" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B27" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="B30" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B28" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B29" t="s">
+      <c r="B31" t="s">
         <v>59</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C31" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B30" t="s">
+    <row r="32" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" t="s">
         <v>60</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C32" s="2" t="s">
         <v>102</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B31" t="s">
-        <v>61</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B32" t="s">
-        <v>62</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B33" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B34" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B35" t="s">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B36" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B37" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B38" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B39" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B40" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B41" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B42" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B43" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B44" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B45" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B46" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B47" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B50" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B51" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B52" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B53" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B54" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B55" t="s">
-        <v>68</v>
+        <v>19</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B56" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B57" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B58" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B59" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B60" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B61" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B62" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B63" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B64" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B65" t="s">
-        <v>29</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>137</v>
+        <v>28</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>30</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>138</v>
+        <v>29</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B67" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B68" t="s">
-        <v>67</v>
+        <v>142</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B69" t="s">
         <v>66</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B70" t="s">
+        <v>65</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/Name.xlsx
+++ b/Name.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\我的資料_路亞國際學校\02A.電腦課程\4000 Essential English Words 題庫系統 1.2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{224ACEBB-53B5-4A48-8DD3-73E8ADF4F33C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E60417B-0F45-493F-89EF-16225E5034AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7DCBFBB1-30D6-49BD-98B1-80C988443001}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="143">
   <si>
     <t>Jayden Lee</t>
   </si>
@@ -86,9 +86,6 @@
     <t>Olivia Huang</t>
   </si>
   <si>
-    <t>Chi Chi Tsai</t>
-  </si>
-  <si>
     <t>Sean Liao</t>
   </si>
   <si>
@@ -171,9 +168,6 @@
   </si>
   <si>
     <t>Shannon Liu</t>
-  </si>
-  <si>
-    <t>Ray Lin</t>
   </si>
   <si>
     <t>Grace Yeh</t>
@@ -242,10 +236,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Joe Lin</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>HR</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -428,9 +418,6 @@
     <t>黃烱榕</t>
   </si>
   <si>
-    <t>林晉有</t>
-  </si>
-  <si>
     <t>鄭川恩</t>
   </si>
   <si>
@@ -487,6 +474,14 @@
   </si>
   <si>
     <t>Lucas Lu</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Chi Chi Tsai</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ray Lin</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -898,7 +893,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{623AE36C-F2A7-441C-93D3-E708820A8AF6}">
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.125" bestFit="1" customWidth="1"/>
@@ -907,772 +902,761 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>142</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B22" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B24" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B26" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B31" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B32" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B31" t="s">
-        <v>59</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B32" t="s">
-        <v>60</v>
-      </c>
       <c r="C32" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B33" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B34" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B35" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B36" t="s">
         <v>0</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B37" t="s">
         <v>1</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B38" t="s">
         <v>2</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B39" t="s">
         <v>3</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B40" t="s">
         <v>4</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B41" t="s">
         <v>5</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B42" t="s">
         <v>6</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B43" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B44" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B45" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B46" t="s">
         <v>10</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B47" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B48" t="s">
         <v>12</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B50" t="s">
         <v>14</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B51" t="s">
         <v>15</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B52" t="s">
-        <v>16</v>
+        <v>141</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B53" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B54" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B55" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B56" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B57" t="s">
         <v>20</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B58" t="s">
         <v>21</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B59" t="s">
         <v>22</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B60" t="s">
         <v>23</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B61" t="s">
         <v>24</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B62" t="s">
         <v>25</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B63" t="s">
         <v>26</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B64" t="s">
         <v>27</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B65" t="s">
         <v>28</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>135</v>
+      <c r="C65" s="3" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B66" t="s">
         <v>29</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>136</v>
+      <c r="C66" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B67" t="s">
-        <v>30</v>
+        <v>138</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>142</v>
+        <v>64</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B69" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B70" t="s">
-        <v>65</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/Name.xlsx
+++ b/Name.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\我的資料_路亞國際學校\02A.電腦課程\4000 Essential English Words 題庫系統 1.2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\我的資料_路亞國際學校\02A.電腦課程\4000 Essential English Words 題庫系統 1.3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E60417B-0F45-493F-89EF-16225E5034AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B351BE1-9523-4971-BB6C-4B7C50EDB915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{7DCBFBB1-30D6-49BD-98B1-80C988443001}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="141">
   <si>
     <t>Jayden Lee</t>
   </si>
@@ -60,9 +60,6 @@
   </si>
   <si>
     <t>Dora Chan</t>
-  </si>
-  <si>
-    <t>Ian Kao</t>
   </si>
   <si>
     <t>Queenie Huang</t>
@@ -379,9 +376,6 @@
   </si>
   <si>
     <t>詹采甯</t>
-  </si>
-  <si>
-    <t>高翌恩</t>
   </si>
   <si>
     <t>黃妍婷</t>
@@ -893,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{623AE36C-F2A7-441C-93D3-E708820A8AF6}">
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C68"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.125" bestFit="1" customWidth="1"/>
@@ -902,497 +896,497 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B16" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B27" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B33" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B34" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B36" t="s">
         <v>0</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B37" t="s">
         <v>1</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B38" t="s">
         <v>2</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B39" t="s">
         <v>3</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B40" t="s">
         <v>4</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B41" t="s">
         <v>5</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B42" t="s">
         <v>6</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B43" t="s">
         <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B44" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B45" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -1403,172 +1397,172 @@
         <v>10</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B47" t="s">
         <v>11</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B48" t="s">
         <v>12</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B50" t="s">
         <v>14</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B51" t="s">
-        <v>15</v>
+        <v>139</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B52" t="s">
-        <v>141</v>
+        <v>15</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B53" t="s">
         <v>16</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B54" t="s">
         <v>17</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B55" t="s">
         <v>18</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B56" t="s">
         <v>19</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B57" t="s">
         <v>20</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B58" t="s">
         <v>21</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B59" t="s">
         <v>22</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B60" t="s">
         <v>23</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B61" t="s">
         <v>24</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -1579,84 +1573,73 @@
         <v>25</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B63" t="s">
         <v>26</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B64" t="s">
         <v>27</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>131</v>
+      <c r="C64" s="3" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B65" t="s">
         <v>28</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>132</v>
+      <c r="C65" s="2" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B66" t="s">
-        <v>29</v>
+        <v>136</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B67" t="s">
-        <v>138</v>
+        <v>63</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B68" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B69" t="s">
-        <v>63</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
